--- a/data.mn/public/datasets/bop-fdi-net.xlsx
+++ b/data.mn/public/datasets/bop-fdi-net.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2535,4 +2536,2134 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B211"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>сар</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>утга</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-12.353</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2009-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-41.885</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2009-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-47.791</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2009-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>8.862</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2009-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.6870000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2009-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-18.551</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-52.16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-52.982</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-65.846</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-169.657</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-60.789</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-55.965</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2010-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-59.423</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2010-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-62.874</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2010-03</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-71.88500000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2010-04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-183.296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2010-05</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-81.72799999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2010-06</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-161.441</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2010-07</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-74.20699999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2010-08</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-198.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2010-09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-168.454</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2010-10</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-209.198</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2010-11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-155.573</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2010-12</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-202.716</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2011-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-330.944</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2011-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-327.108</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2011-03</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-315.806</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2011-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-369.612</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2011-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-398.545</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2011-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-446.044</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2011-07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-380.469</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-293.753</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2011-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-314.22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-474.619</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2011-11</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-398.738</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-426.742</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2012-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-332.469</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2012-02</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-357.81</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2012-03</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-376.588</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2012-04</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-447.038</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2012-05</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-462.328</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2012-06</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-438.179</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2012-07</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>-518.49</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>-467.248</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>-472.587</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2012-10</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>-135.82</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2012-11</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>-62.035</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2012-12</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>-137.226</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>-280.522</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>-280.736</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-278.622</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-152.016</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>-113.915</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-125.615</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>-124.901</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>-137.394</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>-104.842</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>-129.171</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>-149.374</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>-141.608</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>-150.419</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2014-02</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-67.483</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2014-03</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>-54.488</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-39.237</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2014-05</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2014-06</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>-12.739</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>-55.484</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>-52.439</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>-44.265</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>114.402</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4.077</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>49.425</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2015-02</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>28.551</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2015-03</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>35.484</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2015-04</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>10.332</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2015-05</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>-39.164</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2015-06</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>-28.076</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2015-07</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>6.448</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>-18.156</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2015-09</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>40.052</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2015-10</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>-33.946</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2015-11</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>-64.041</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2015-12</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>-69.821</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2016-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>-103.508</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2016-02</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>-37.179</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2016-03</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>-72.879</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2016-04</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>-74.20999999999999</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2016-05</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>3862.903</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2016-06</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>745.2430000000001</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>-26.198</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2016-09</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>-23.949</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>-33.869</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>13.509</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>-73.386</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>-67.227</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2017-02</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>-41.721</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>-28.982</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>-103.607</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2017-05</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>-105.622</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2017-06</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>-185.011</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2017-07</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>-165.371</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>-152.761</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2017-09</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>-121.329</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2017-10</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>-91.447</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2017-11</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>-161.144</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2017-12</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>-221.514</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>-130.62</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>-159.528</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>-187.934</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>-112.205</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>-154.467</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>-264.426</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>-168.512</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>-125.117</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>-174.191</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>-191.224</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>-107.338</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>-361.133</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>-223.096</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>-158.63</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>-100.094</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>-144.347</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>-150.699</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>-277.051</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>-170.506</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>-135.058</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>-186.56</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>-202.499</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>-158.167</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>-409.664</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>-91.378</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>-77.18899999999999</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>-200.623</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>-137.956</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>-109.601</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>-307.49</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>-104.316</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>-89.336</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>-117.401</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>-81.002</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>-138.695</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>-238.161</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>-122.807</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>-142.319</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>-340.718</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>-114.554</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>-92.422</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>-107.34</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>-184.907</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>-188.79</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>-159.048</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>-210.365</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>-201.9</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>-194.852</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>-233.331</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>-62.445</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>-96.33499999999999</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>-40.168</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>-46.132</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>-37.471</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>-177.072</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>-169.037</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>-165.961</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>-169.694</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>-201.24</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>-1029.551</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>-89.056</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>-65.511</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>-153.49</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>-139.703</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>-130.238</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>-270.291</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>-202.004</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>-171.107</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>-172.085</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>-172.979</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>-177.715</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>-427.456</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>-292.703</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>-258.952</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>-122.646</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>-325.009</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>-266.163</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>-366.886</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>-156.991</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>-95.84699999999999</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>-161.564</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>-165.249</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>-120.605</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>-394.094</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>-137.6</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>-125.65</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>-140.04</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>-176.93</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>-203.01</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>-133.1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>-310.78</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>-327.95</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>-264.95</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>-487.82</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>-460.56</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>28.71</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>-402.369</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>-432.018</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>-417.62</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>-505.599</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>-497.045</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1021.981</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.mn/public/datasets/bop-fdi-net.xlsx
+++ b/data.mn/public/datasets/bop-fdi-net.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B211"/>
+  <dimension ref="A1:B213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-505.599</v>
+        <v>-477.318</v>
       </c>
     </row>
     <row r="210">
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-497.045</v>
+        <v>-468.958</v>
       </c>
     </row>
     <row r="211">
@@ -2530,7 +2530,27 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1021.981</v>
+        <v>1012.557</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>-418.175</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>-398.094</v>
       </c>
     </row>
   </sheetData>
@@ -2544,7 +2564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B211"/>
+  <dimension ref="A1:B213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4640,7 +4660,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-505.599</v>
+        <v>-477.318</v>
       </c>
     </row>
     <row r="210">
@@ -4650,7 +4670,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-497.045</v>
+        <v>-468.958</v>
       </c>
     </row>
     <row r="211">
@@ -4660,7 +4680,27 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1021.981</v>
+        <v>1012.557</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>-418.175</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>-398.094</v>
       </c>
     </row>
   </sheetData>
